--- a/data/trans_orig/P37C3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37C3_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de que las vacunas son efectivas en 2023</t>
+          <t>Población según la creencia de que las vacunas son efectivas en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>8971</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25444</t>
+          <t>25974</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46165</t>
+          <t>47063</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35672</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63648</t>
+          <t>67445</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66760</t>
+          <t>65852</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100566</t>
+          <t>102473</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65788</t>
+          <t>65380</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97433</t>
+          <t>96473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104651</t>
+          <t>103417</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136060</t>
+          <t>134936</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179546</t>
+          <t>179529</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>224352</t>
+          <t>222488</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359788</t>
+          <t>358370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>394396</t>
+          <t>395077</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>551713</t>
+          <t>551657</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>589982</t>
+          <t>589744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>921431</t>
+          <t>920475</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>976546</t>
+          <t>972522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>16216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22219</t>
+          <t>23352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11069</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29095</t>
+          <t>28941</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,47 +1575,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>30660</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>20303</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>42788</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>30660</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>20794</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>44185</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78235</t>
+          <t>81092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143991</t>
+          <t>147828</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50146</t>
+          <t>50483</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94421</t>
+          <t>92349</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>146678</t>
+          <t>146696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>227182</t>
+          <t>224342</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>337722</t>
+          <t>344160</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>573667</t>
+          <t>570604</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>333329</t>
+          <t>329885</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>507820</t>
+          <t>507895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>746837</t>
+          <t>754613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1054421</t>
+          <t>1057188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1546641</t>
+          <t>1546206</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1849777</t>
+          <t>1833903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1623229</t>
+          <t>1618425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1833536</t>
+          <t>1831859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3196159</t>
+          <t>3205701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3570856</t>
+          <t>3584324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,52%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>15225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>11361</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31736</t>
+          <t>32311</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37781</t>
+          <t>35532</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30825</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59661</t>
+          <t>58847</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>130631</t>
+          <t>129486</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175611</t>
+          <t>176670</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105968</t>
+          <t>105513</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>140549</t>
+          <t>139504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>248392</t>
+          <t>247556</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>303594</t>
+          <t>304354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>438015</t>
+          <t>439671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>486891</t>
+          <t>488052</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>487086</t>
+          <t>489241</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>526595</t>
+          <t>527282</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>939235</t>
+          <t>939744</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1002115</t>
+          <t>1001519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,73%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19934</t>
+          <t>19874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12014</t>
+          <t>12577</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22170</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46836</t>
+          <t>47620</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>14114</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30934</t>
+          <t>30532</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41417</t>
+          <t>42123</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70574</t>
+          <t>71359</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>136285</t>
+          <t>131745</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>207083</t>
+          <t>207661</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112224</t>
+          <t>112173</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>170267</t>
+          <t>169007</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>267042</t>
+          <t>261581</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>358023</t>
+          <t>351807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>565889</t>
+          <t>537329</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>805921</t>
+          <t>807662</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>545120</t>
+          <t>564001</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>744988</t>
+          <t>747448</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1213872</t>
+          <t>1216580</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1521446</t>
+          <t>1521335</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2390396</t>
+          <t>2385416</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2693333</t>
+          <t>2717377</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2702181</t>
+          <t>2701672</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2947818</t>
+          <t>2938418</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5122866</t>
+          <t>5131380</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5510415</t>
+          <t>5504605</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37C3_2023-Estudios-trans_orig.xlsx
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>429</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,22 +795,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -838,22 +838,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15259</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23105</t>
+          <t>24790</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34991</t>
+          <t>43094</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>31425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47063</t>
+          <t>56087</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45682</t>
+          <t>46007</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36000</t>
+          <t>37533</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67445</t>
+          <t>57021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>80673</t>
+          <t>89101</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65852</t>
+          <t>75331</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>102473</t>
+          <t>106327</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80833</t>
+          <t>94945</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65380</t>
+          <t>79370</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96473</t>
+          <t>113402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>119566</t>
+          <t>133850</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103417</t>
+          <t>117740</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>134936</t>
+          <t>152206</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>200399</t>
+          <t>228794</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179529</t>
+          <t>205999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>222488</t>
+          <t>253703</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>377049</t>
+          <t>412402</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>358370</t>
+          <t>390105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395077</t>
+          <t>430535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>571841</t>
+          <t>623767</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>551657</t>
+          <t>603974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>589744</t>
+          <t>642622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>948889</t>
+          <t>1036169</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>920475</t>
+          <t>1010398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>972522</t>
+          <t>1065016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,65%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>502939</t>
+          <t>560889</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>502939</t>
+          <t>560889</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>502939</t>
+          <t>560889</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>743764</t>
+          <t>810718</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>743764</t>
+          <t>810718</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>743764</t>
+          <t>810718</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1246702</t>
+          <t>1371608</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1246702</t>
+          <t>1371608</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1246702</t>
+          <t>1371608</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,57 +1442,57 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16216</t>
+          <t>16060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>6283</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>22822</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>12255</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>6253</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>23352</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1520,102 +1520,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18278</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10217</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28941</t>
+          <t>34293</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>12790</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7902</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>19445</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>35122</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>24472</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>48098</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>12383</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>7520</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>20694</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>30660</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>20303</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>42788</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>115871</t>
+          <t>135795</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81092</t>
+          <t>110416</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147828</t>
+          <t>161969</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71178</t>
+          <t>80561</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50483</t>
+          <t>63686</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92349</t>
+          <t>101880</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>187049</t>
+          <t>216355</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>146696</t>
+          <t>182912</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>224342</t>
+          <t>251012</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>494254</t>
+          <t>544799</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>344160</t>
+          <t>500073</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>570604</t>
+          <t>594743</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>442401</t>
+          <t>495783</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>329885</t>
+          <t>460506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>507895</t>
+          <t>533027</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>936655</t>
+          <t>1040582</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>754613</t>
+          <t>983123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1057188</t>
+          <t>1103176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1642427</t>
+          <t>1505923</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1546206</t>
+          <t>1452488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1833903</t>
+          <t>1555704</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1698330</t>
+          <t>1567078</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1618425</t>
+          <t>1526776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1831859</t>
+          <t>1606338</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3340757</t>
+          <t>3073000</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3205701</t>
+          <t>3003765</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3584324</t>
+          <t>3132153</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2276670</t>
+          <t>2214216</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2276670</t>
+          <t>2214216</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2276670</t>
+          <t>2214216</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2230707</t>
+          <t>2163706</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2230707</t>
+          <t>2163706</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2230707</t>
+          <t>2163706</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4507377</t>
+          <t>4377921</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4507377</t>
+          <t>4377921</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4507377</t>
+          <t>4377921</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>9755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15225</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,22 +2272,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>18396</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>22761</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13257</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32311</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,27 +2350,27 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>26246</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14503</t>
+          <t>17024</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35532</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>43441</t>
+          <t>49007</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>31058</t>
+          <t>36191</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58847</t>
+          <t>65796</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>152145</t>
+          <t>171870</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>129486</t>
+          <t>148339</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>176670</t>
+          <t>197399</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>121972</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105513</t>
+          <t>118372</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139504</t>
+          <t>156286</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>274117</t>
+          <t>309148</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>247556</t>
+          <t>278438</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>304354</t>
+          <t>341038</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>463922</t>
+          <t>506518</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>439671</t>
+          <t>479918</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>488052</t>
+          <t>532378</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>508278</t>
+          <t>562749</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>489241</t>
+          <t>541231</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>527282</t>
+          <t>582155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>972200</t>
+          <t>1069267</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>939744</t>
+          <t>1034816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1001519</t>
+          <t>1100076</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>658674</t>
+          <t>732992</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>658674</t>
+          <t>732992</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>658674</t>
+          <t>732992</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1305297</t>
+          <t>1444579</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1305297</t>
+          <t>1444579</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1305297</t>
+          <t>1444579</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20241</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>11321</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19874</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,17 +2841,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>13157</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>32566</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>38805</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23168</t>
+          <t>27686</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47620</t>
+          <t>53222</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>15818</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30532</t>
+          <t>32054</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>54540</t>
+          <t>61582</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42123</t>
+          <t>47398</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71359</t>
+          <t>77240</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>171711</t>
+          <t>201650</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>131745</t>
+          <t>172040</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>207661</t>
+          <t>235444</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>139451</t>
+          <t>152814</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112173</t>
+          <t>130698</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>169007</t>
+          <t>177579</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>311163</t>
+          <t>354464</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>261581</t>
+          <t>315537</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>351807</t>
+          <t>397388</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>727232</t>
+          <t>811613</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>537329</t>
+          <t>757948</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>807662</t>
+          <t>870073</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>683939</t>
+          <t>766911</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>564001</t>
+          <t>725088</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>747448</t>
+          <t>808269</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1411171</t>
+          <t>1578525</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1216580</t>
+          <t>1510452</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1521335</t>
+          <t>1650942</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2483398</t>
+          <t>2424843</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2385416</t>
+          <t>2359316</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2717377</t>
+          <t>2481238</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2778449</t>
+          <t>2753593</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2701672</t>
+          <t>2707384</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2938418</t>
+          <t>2799556</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5261847</t>
+          <t>5178436</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5131380</t>
+          <t>5101155</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5504605</t>
+          <t>5264388</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3426232</t>
+          <t>3486692</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3426232</t>
+          <t>3486692</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3426232</t>
+          <t>3486692</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3633145</t>
+          <t>3707415</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3633145</t>
+          <t>3707415</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3633145</t>
+          <t>3707415</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7059377</t>
+          <t>7194108</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7059377</t>
+          <t>7194108</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7059377</t>
+          <t>7194108</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
